--- a/artfynd/A 5855-2024 artfynd.xlsx
+++ b/artfynd/A 5855-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5855-2024 artfynd.xlsx
+++ b/artfynd/A 5855-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89818793</v>
+        <v>89818792</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600647.2267256121</v>
+        <v>600590</v>
       </c>
       <c r="R2" t="n">
-        <v>6504332.824961304</v>
+        <v>6504329</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,19 +747,9 @@
           <t>2020-06-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-06-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89818805</v>
+        <v>89818794</v>
       </c>
       <c r="B3" t="n">
-        <v>57585</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208242</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601197.8402817376</v>
+        <v>600843</v>
       </c>
       <c r="R3" t="n">
-        <v>6504468.875346724</v>
+        <v>6504381</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -873,21 +853,11 @@
           <t>2020-06-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-06-11</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>JMN0065 Calluna AB</t>
@@ -901,11 +871,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>15 individer. Lekvatten</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -925,12 +890,7 @@
         <v>89818798</v>
       </c>
       <c r="B4" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601007.7674954459</v>
+        <v>601008</v>
       </c>
       <c r="R4" t="n">
-        <v>6504400.971942966</v>
+        <v>6504401</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -999,19 +959,9 @@
           <t>2020-06-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-06-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1040,6 +990,758 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>89818793</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Oxelösund Hedenlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>600647</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6504333</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tunaberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>JMN0065 Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>89818799</v>
+      </c>
+      <c r="B6" t="n">
+        <v>43464</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>201116</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Berggräsfjäril</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lasiommata petropolitana</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Oxelösund Hedenlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>601101</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6504461</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tunaberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>JMN0065 Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Berggräsfjäril</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>89818805</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58826</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Oxelösund Hedenlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>601198</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6504469</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tunaberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>JMN0065 Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>15 individer. Lekvatten</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>89818801</v>
+      </c>
+      <c r="B8" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Oxelösund Hedenlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>601132</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6504469</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tunaberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>JMN0065 Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>89818804</v>
+      </c>
+      <c r="B9" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Oxelösund Hedenlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>601188</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6504474</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tunaberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>JMN0065 Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>89818800</v>
+      </c>
+      <c r="B10" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Oxelösund Hedenlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>601107</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6504461</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tunaberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>JMN0065 Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>89818806</v>
+      </c>
+      <c r="B11" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Oxelösund Hedenlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>601224</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6504456</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tunaberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>JMN0065 Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5855-2024 artfynd.xlsx
+++ b/artfynd/A 5855-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89818799</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89818805</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89818792</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89818794</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89818798</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89818801</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1424,6 +1459,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89818804</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1530,6 +1570,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89818793</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1636,6 +1681,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89818800</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,8 +1792,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89818806</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>